--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
@@ -1111,7 +1111,7 @@
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Toda sexta (10 minutos)</t>
+          <t>Toda sexta (3 minutos)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Na aba Dados, coluna C, escreva o limite de cada indicador (ex.: ocupação de 75 %, taxa de falta de 6 %, glosa de 4 %, inadimplência de 8 %) e diga se maior ou menor é melhor. Linha sem limite fica informativa.</t>
+          <t>Na aba Dados, coluna C, escreva o limite de cada indicador (ex.: ocupação de 75 %, taxa de falta de 6 %, glosa de 4 %, inadimplência de 8 %) e diga se maior ou menor é melhor. Linha sem limite fica informativa — é o caso de convênio a receber e dos orçamentos em aberto, que sozinhos não dizem se a clínica vai bem ou mal.</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="12">
         <f>IF(Dados!$B$9="","—",Dados!$B$9)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" s="8" t="n"/>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="13">
         <f>IF(Dados!$B$10="","—",Dados!$B$10)</f>
-        <v>21570</v>
+        <v>21920</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="13">
@@ -1397,7 +1397,7 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="13">
         <f>IF(Dados!$B$12="","—",Dados!$B$12)</f>
-        <v>7940</v>
+        <v>8290</v>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="13">
@@ -1452,12 +1452,12 @@
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="13">
         <f>IF(Dados!$B$16="","—",Dados!$B$16)</f>
-        <v>4550</v>
+        <v>3775</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="11">
         <f>IF(Dados!$B$17="","—",Dados!$B$17)</f>
-        <v>0.1045</v>
+        <v>0.0936</v>
       </c>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="12">
@@ -1635,7 +1635,7 @@
       <c r="B20" s="16" t="n"/>
       <c r="C20" s="24">
         <f>IF(Dados!B9="","—",Dados!B9)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="24">
         <f>IF(Dados!C9="","—",Dados!C9)</f>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="F20" s="24">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$F$5:$F$16,Config!$B$8-1)="","—",INDEX(Histórico!$F$5:$F$16,Config!$B$8-1)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="22">
         <f>(IF(OR(C20="—",F20="—",F20=0),"—",(C20-F20)/ABS(F20)))</f>
-        <v>1.33333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1662,7 +1662,7 @@
       <c r="B21" s="16" t="n"/>
       <c r="C21" s="25">
         <f>IF(Dados!B10="","—",Dados!B10)</f>
-        <v>21570</v>
+        <v>21920</v>
       </c>
       <c r="D21" s="25" t="str">
         <f>IF(Dados!C10="","—",Dados!C10)</f>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="F21" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$G$5:$G$16,Config!$B$8-1)="","—",INDEX(Histórico!$G$5:$G$16,Config!$B$8-1)))</f>
-        <v>50336</v>
+        <v>49651</v>
       </c>
       <c r="G21" s="22" t="str">
         <f>IF(Config!$B$10&lt;&gt;"Sim","no fechamento",IF(OR(C21="—",F21="—",F21=0),"—",(C21-F21)/ABS(F21)))</f>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="F22" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$H$5:$H$16,Config!$B$8-1)="","—",INDEX(Histórico!$H$5:$H$16,Config!$B$8-1)))</f>
-        <v>41620.12</v>
+        <v>41660.12</v>
       </c>
       <c r="G22" s="22" t="str">
         <f>IF(Config!$B$10&lt;&gt;"Sim","no fechamento",IF(OR(C22="—",F22="—",F22=0),"—",(C22-F22)/ABS(F22)))</f>
@@ -1716,7 +1716,7 @@
       <c r="B23" s="16" t="n"/>
       <c r="C23" s="25">
         <f>IF(Dados!B12="","—",Dados!B12)</f>
-        <v>7940</v>
+        <v>8290</v>
       </c>
       <c r="D23" s="25" t="str">
         <f>IF(Dados!C12="","—",Dados!C12)</f>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="F23" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$I$5:$I$16,Config!$B$8-1)="","—",INDEX(Histórico!$I$5:$I$16,Config!$B$8-1)))</f>
-        <v>8715.88</v>
+        <v>7990.88</v>
       </c>
       <c r="G23" s="22" t="str">
         <f>IF(Config!$B$10&lt;&gt;"Sim","no fechamento",IF(OR(C23="—",F23="—",F23=0),"—",(C23-F23)/ABS(F23)))</f>
@@ -1824,7 +1824,7 @@
       <c r="B27" s="16" t="n"/>
       <c r="C27" s="25">
         <f>IF(Dados!B16="","—",Dados!B16)</f>
-        <v>4550</v>
+        <v>3775</v>
       </c>
       <c r="D27" s="25">
         <f>IF(Dados!C16="","—",Dados!C16)</f>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="E27" s="19" t="str">
         <f>Dados!F16</f>
-        <v>Fora</v>
+        <v>No alvo</v>
       </c>
       <c r="F27" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$M$5:$M$16,Config!$B$8-1)="","—",INDEX(Histórico!$M$5:$M$16,Config!$B$8-1)))</f>
-        <v>4040</v>
+        <v>4005</v>
       </c>
       <c r="G27" s="22">
         <f>(IF(OR(C27="—",F27="—",F27=0),"—",(C27-F27)/ABS(F27)))</f>
-        <v>0.126237623762376</v>
+        <v>-0.0574282147315855</v>
       </c>
     </row>
     <row r="28">
@@ -1851,7 +1851,7 @@
       <c r="B28" s="16" t="n"/>
       <c r="C28" s="23">
         <f>IF(Dados!B17="","—",Dados!B17)</f>
-        <v>0.1045</v>
+        <v>0.0936</v>
       </c>
       <c r="D28" s="23">
         <f>IF(Dados!C17="","—",Dados!C17)</f>
@@ -1863,11 +1863,11 @@
       </c>
       <c r="F28" s="23">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$N$5:$N$16,Config!$B$8-1)="","—",INDEX(Histórico!$N$5:$N$16,Config!$B$8-1)))</f>
-        <v>0.0983</v>
+        <v>0.1047</v>
       </c>
       <c r="G28" s="20">
         <f>(IF(OR(C28="—",F28="—"),"—",(C28-F28)*100))</f>
-        <v>0.62</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="29">
@@ -1890,11 +1890,11 @@
       </c>
       <c r="F29" s="24">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$O$5:$O$16,Config!$B$8-1)="","—",INDEX(Histórico!$O$5:$O$16,Config!$B$8-1)))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G29" s="22">
         <f>(IF(OR(C29="—",F29="—",F29=0),"—",(C29-F29)/ABS(F29)))</f>
-        <v>0.2</v>
+        <v>-0.142857142857143</v>
       </c>
     </row>
     <row r="30">
@@ -1907,21 +1907,21 @@
         <f>IF(Dados!B19="","—",Dados!B19)</f>
         <v>3460</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="25" t="str">
         <f>IF(Dados!C19="","—",Dados!C19)</f>
-        <v>5000</v>
+        <v>—</v>
       </c>
       <c r="E30" s="19" t="str">
         <f>Dados!F19</f>
-        <v>Fora</v>
+        <v>Informativo</v>
       </c>
       <c r="F30" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$P$5:$P$16,Config!$B$8-1)="","—",INDEX(Histórico!$P$5:$P$16,Config!$B$8-1)))</f>
-        <v>1730</v>
+        <v>2700</v>
       </c>
       <c r="G30" s="22">
         <f>(IF(OR(C30="—",F30="—",F30=0),"—",(C30-F30)/ABS(F30)))</f>
-        <v>1</v>
+        <v>0.281481481481482</v>
       </c>
     </row>
     <row r="31"/>
@@ -2331,6 +2331,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Esta planilha só guarda totais: são 12 linhas de Dados e 12 de Histórico por ano, e nada envelhece. As planilhas de lançamento (01, 02, 09, 13, 14, 15, 16) têm um número fixo de linhas — cada "Como usar" diz quantas e como estender ou virar o ano.</t>
+        </is>
+      </c>
       <c r="D12" s="31" t="inlineStr">
         <is>
           <t>Agosto</t>
@@ -2549,7 +2554,7 @@
         </is>
       </c>
       <c r="B9" s="39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="39" t="n">
         <v>8</v>
@@ -2576,7 +2581,7 @@
         </is>
       </c>
       <c r="B10" s="40" t="n">
-        <v>21570</v>
+        <v>21920</v>
       </c>
       <c r="C10" s="40" t="n"/>
       <c r="D10" s="35" t="inlineStr"/>
@@ -2619,7 +2624,7 @@
       </c>
       <c r="B12" s="25">
         <f>IF(OR(B10="",B11=""),"",B10-B11)</f>
-        <v>7940</v>
+        <v>8290</v>
       </c>
       <c r="C12" s="40" t="n"/>
       <c r="D12" s="35" t="inlineStr"/>
@@ -2715,7 +2720,7 @@
         </is>
       </c>
       <c r="B16" s="40" t="n">
-        <v>4550</v>
+        <v>3775</v>
       </c>
       <c r="C16" s="40" t="n">
         <v>4000</v>
@@ -2732,7 +2737,7 @@
       </c>
       <c r="F16" s="19" t="str">
         <f>IF(OR(B16="",C16=""),"Informativo",IF(D16="Menor é melhor",IF(B16&lt;=C16,"No alvo",IF(B16&lt;=C16*1.1+(C16=0)*0.0001,"Perto","Fora")),IF(B16&gt;=C16,"No alvo",IF(B16&gt;=C16*0.9,"Perto","Fora"))))</f>
-        <v>Fora</v>
+        <v>No alvo</v>
       </c>
     </row>
     <row r="17">
@@ -2742,7 +2747,7 @@
         </is>
       </c>
       <c r="B17" s="38" t="n">
-        <v>0.1045</v>
+        <v>0.0936</v>
       </c>
       <c r="C17" s="38" t="n">
         <v>0.08</v>
@@ -2792,14 +2797,8 @@
       <c r="B19" s="40" t="n">
         <v>3460</v>
       </c>
-      <c r="C19" s="40" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D19" s="35" t="inlineStr">
-        <is>
-          <t>Maior é melhor</t>
-        </is>
-      </c>
+      <c r="C19" s="40" t="n"/>
+      <c r="D19" s="35" t="inlineStr"/>
       <c r="E19" s="36" t="inlineStr">
         <is>
           <t>15 · Orçamentos (Painel: Em aberto)</t>
@@ -2807,13 +2806,13 @@
       </c>
       <c r="F19" s="19" t="str">
         <f>IF(OR(B19="",C19=""),"Informativo",IF(D19="Menor é melhor",IF(B19&lt;=C19,"No alvo",IF(B19&lt;=C19*1.1+(C19=0)*0.0001,"Perto","Fora")),IF(B19&gt;=C19,"No alvo",IF(B19&gt;=C19*0.9,"Perto","Fora"))))</f>
-        <v>Fora</v>
+        <v>Informativo</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>Linha sem limite fica "Informativo". "Perto" é até 10% do limite. Inadimplência = vencido ÷ (pago + vencido), a mesma conta da planilha 14. Convênio a receber é o que foi enviado e ainda está no prazo: informativo; o problema é o atrasado. Os valores desta sexta valem para o mês escolhido em Config; no fim do mês, copie a coluna B para a linha do mês em Histórico.</t>
+          <t>Linha sem limite fica "Informativo". "Perto" é até 10% do limite. Inadimplência = vencido ÷ (pago + vencido), a mesma conta da planilha 14. Convênio a receber é o que foi enviado e ainda está no prazo: informativo; o problema é o atrasado. Orçamentos em aberto também são informativos: pouco orçamento pendente pode ser bom (fechou tudo) ou ruim (a recepção parou de apresentar) — quem diz é a taxa de aprovação da planilha 15, não o valor parado. Os valores desta sexta valem para o mês escolhido em Config; no fim do mês, copie a coluna B para a linha do mês em Histórico.</t>
         </is>
       </c>
     </row>
@@ -3065,14 +3064,14 @@
       <c r="E7" s="38" t="n"/>
       <c r="F7" s="39" t="n"/>
       <c r="G7" s="40" t="n">
-        <v>47880</v>
+        <v>48330</v>
       </c>
       <c r="H7" s="40" t="n">
         <v>38415.25</v>
       </c>
       <c r="I7" s="25">
         <f>IF(OR(G7="",H7=""),"",G7-H7)</f>
-        <v>9464.75</v>
+        <v>9914.75</v>
       </c>
       <c r="J7" s="40" t="n">
         <v>7836</v>
@@ -3104,14 +3103,14 @@
       <c r="E8" s="38" t="n"/>
       <c r="F8" s="39" t="n"/>
       <c r="G8" s="40" t="n">
-        <v>39590</v>
+        <v>39555</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>41012.7</v>
+        <v>41061.7</v>
       </c>
       <c r="I8" s="25">
         <f>IF(OR(G8="",H8=""),"",G8-H8)</f>
-        <v>-1422.7</v>
+        <v>-1506.7</v>
       </c>
       <c r="J8" s="40" t="n">
         <v>13011</v>
@@ -3126,7 +3125,7 @@
         <v>790</v>
       </c>
       <c r="N8" s="38" t="n">
-        <v>0.0731</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="O8" s="39" t="n"/>
       <c r="P8" s="40" t="n"/>
@@ -3143,14 +3142,14 @@
       <c r="E9" s="38" t="n"/>
       <c r="F9" s="39" t="n"/>
       <c r="G9" s="40" t="n">
-        <v>44760</v>
+        <v>44745</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>39976.12</v>
+        <v>39972.12</v>
       </c>
       <c r="I9" s="25">
         <f>IF(OR(G9="",H9=""),"",G9-H9)</f>
-        <v>4783.88</v>
+        <v>4772.88</v>
       </c>
       <c r="J9" s="40" t="n">
         <v>9973</v>
@@ -3162,10 +3161,10 @@
         <v>0.0494</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>2120</v>
+        <v>2140</v>
       </c>
       <c r="N9" s="38" t="n">
-        <v>0.1152</v>
+        <v>0.119</v>
       </c>
       <c r="O9" s="39" t="n"/>
       <c r="P9" s="40" t="n"/>
@@ -3176,20 +3175,30 @@
           <t>Junho</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n"/>
-      <c r="C10" s="37" t="n"/>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="39" t="n"/>
+      <c r="B10" s="34" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="C10" s="37" t="n">
+        <v>123.6667</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>44.3333</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="G10" s="40" t="n">
-        <v>43855</v>
+        <v>44160</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>41533.91</v>
+        <v>41531.91</v>
       </c>
       <c r="I10" s="25">
         <f>IF(OR(G10="",H10=""),"",G10-H10)</f>
-        <v>2321.09</v>
+        <v>2628.09</v>
       </c>
       <c r="J10" s="40" t="n">
         <v>12239</v>
@@ -3201,16 +3210,16 @@
         <v>0.0931</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>2610</v>
+        <v>2900</v>
       </c>
       <c r="N10" s="38" t="n">
-        <v>0.0946</v>
+        <v>0.1092</v>
       </c>
       <c r="O10" s="39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11">
@@ -3232,17 +3241,17 @@
         <v>0.08749999999999999</v>
       </c>
       <c r="F11" s="39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>53101</v>
+        <v>53461</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>43426.77</v>
+        <v>43566.77</v>
       </c>
       <c r="I11" s="25">
         <f>IF(OR(G11="",H11=""),"",G11-H11)</f>
-        <v>9674.23</v>
+        <v>9894.23</v>
       </c>
       <c r="J11" s="40" t="n">
         <v>13553</v>
@@ -3254,16 +3263,16 @@
         <v>0.0427</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>3380</v>
+        <v>3290</v>
       </c>
       <c r="N11" s="38" t="n">
-        <v>0.0963</v>
+        <v>0.1</v>
       </c>
       <c r="O11" s="39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>2590</v>
+        <v>830</v>
       </c>
     </row>
     <row r="12">
@@ -3285,17 +3294,17 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="F12" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>50336</v>
+        <v>49651</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>41620.12</v>
+        <v>41660.12</v>
       </c>
       <c r="I12" s="25">
         <f>IF(OR(G12="",H12=""),"",G12-H12)</f>
-        <v>8715.88</v>
+        <v>7990.88</v>
       </c>
       <c r="J12" s="40" t="n">
         <v>12077</v>
@@ -3307,16 +3316,16 @@
         <v>0.0562</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>4040</v>
+        <v>4005</v>
       </c>
       <c r="N12" s="38" t="n">
-        <v>0.0983</v>
+        <v>0.1047</v>
       </c>
       <c r="O12" s="39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>1730</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="13">
@@ -3338,17 +3347,17 @@
         <v>0.0531</v>
       </c>
       <c r="F13" s="39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>21570</v>
+        <v>21920</v>
       </c>
       <c r="H13" s="40" t="n">
         <v>13630</v>
       </c>
       <c r="I13" s="25">
         <f>IF(OR(G13="",H13=""),"",G13-H13)</f>
-        <v>7940</v>
+        <v>8290</v>
       </c>
       <c r="J13" s="40" t="n">
         <v>15758</v>
@@ -3360,10 +3369,10 @@
         <v>0.0286</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>4550</v>
+        <v>3775</v>
       </c>
       <c r="N13" s="38" t="n">
-        <v>0.1045</v>
+        <v>0.0936</v>
       </c>
       <c r="O13" s="39" t="n">
         <v>6</v>
@@ -3450,7 +3459,7 @@
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>A linha do mês escolhido em Config fica destacada. Setembro repete os valores da aba Dados (mês em andamento, até 11/09). Entrou e Saiu = Painel mensal da planilha 09 (caixa real). Agenda: o registro na planilha 01 começou em julho; antes fica em branco. Orçamentos: o funil (15) começou em junho. Convênio, vencido e inadimplência: o que a clínica copiou no fim de cada mês. Glosa no mês = dos lotes pagos naquele mês (no Dados, o acumulado do ano).</t>
+          <t>A linha do mês escolhido em Config fica destacada. Setembro repete os valores da aba Dados (mês em andamento, até 11/09). Entrou e Saiu = Painel mensal da planilha 09 (caixa real). Agenda: o registro na planilha 01 começou em junho; antes fica em branco. Orçamentos: o funil (15) começou em junho. Convênio, vencido e inadimplência: o que a clínica copiou no fim de cada mês. Glosa no mês = dos lotes pagos naquele mês (no Dados, o acumulado do ano).</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E20" s="19" t="str">
         <f>Dados!F9</f>
-        <v>No alvo</v>
+        <v>Perto</v>
       </c>
       <c r="F20" s="24">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$F$5:$F$16,Config!$B$8-1)="","—",INDEX(Histórico!$F$5:$F$16,Config!$B$8-1)))</f>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="F5" s="19" t="str">
-        <f>IF(OR(B5="",C5=""),"Informativo",IF(D5="Menor é melhor",IF(B5&lt;=C5,"No alvo",IF(B5&lt;=C5*1.1+(C5=0)*0.0001,"Perto","Fora")),IF(B5&gt;=C5,"No alvo",IF(B5&gt;=C5*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B5="",C5=""),"Informativo",IF(D5="Menor é melhor",IF(B5&lt;C5,"No alvo",IF(B5&lt;=C5*1.1+(C5=0)*0.0001,"Perto","Fora")),IF(B5&gt;C5,"No alvo",IF(B5&gt;=C5*0.9,"Perto","Fora"))))</f>
         <v>No alvo</v>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="F6" s="19" t="str">
-        <f>IF(OR(B6="",C6=""),"Informativo",IF(D6="Menor é melhor",IF(B6&lt;=C6,"No alvo",IF(B6&lt;=C6*1.1+(C6=0)*0.0001,"Perto","Fora")),IF(B6&gt;=C6,"No alvo",IF(B6&gt;=C6*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B6="",C6=""),"Informativo",IF(D6="Menor é melhor",IF(B6&lt;C6,"No alvo",IF(B6&lt;=C6*1.1+(C6=0)*0.0001,"Perto","Fora")),IF(B6&gt;C6,"No alvo",IF(B6&gt;=C6*0.9,"Perto","Fora"))))</f>
         <v>Informativo</v>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F7" s="19" t="str">
-        <f>IF(OR(B7="",C7=""),"Informativo",IF(D7="Menor é melhor",IF(B7&lt;=C7,"No alvo",IF(B7&lt;=C7*1.1+(C7=0)*0.0001,"Perto","Fora")),IF(B7&gt;=C7,"No alvo",IF(B7&gt;=C7*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B7="",C7=""),"Informativo",IF(D7="Menor é melhor",IF(B7&lt;C7,"No alvo",IF(B7&lt;=C7*1.1+(C7=0)*0.0001,"Perto","Fora")),IF(B7&gt;C7,"No alvo",IF(B7&gt;=C7*0.9,"Perto","Fora"))))</f>
         <v>Informativo</v>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="F8" s="19" t="str">
-        <f>IF(OR(B8="",C8=""),"Informativo",IF(D8="Menor é melhor",IF(B8&lt;=C8,"No alvo",IF(B8&lt;=C8*1.1+(C8=0)*0.0001,"Perto","Fora")),IF(B8&gt;=C8,"No alvo",IF(B8&gt;=C8*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B8="",C8=""),"Informativo",IF(D8="Menor é melhor",IF(B8&lt;C8,"No alvo",IF(B8&lt;=C8*1.1+(C8=0)*0.0001,"Perto","Fora")),IF(B8&gt;C8,"No alvo",IF(B8&gt;=C8*0.9,"Perto","Fora"))))</f>
         <v>No alvo</v>
       </c>
     </row>
@@ -2570,8 +2570,8 @@
         </is>
       </c>
       <c r="F9" s="19" t="str">
-        <f>IF(OR(B9="",C9=""),"Informativo",IF(D9="Menor é melhor",IF(B9&lt;=C9,"No alvo",IF(B9&lt;=C9*1.1+(C9=0)*0.0001,"Perto","Fora")),IF(B9&gt;=C9,"No alvo",IF(B9&gt;=C9*0.9,"Perto","Fora"))))</f>
-        <v>No alvo</v>
+        <f>IF(OR(B9="",C9=""),"Informativo",IF(D9="Menor é melhor",IF(B9&lt;C9,"No alvo",IF(B9&lt;=C9*1.1+(C9=0)*0.0001,"Perto","Fora")),IF(B9&gt;C9,"No alvo",IF(B9&gt;=C9*0.9,"Perto","Fora"))))</f>
+        <v>Perto</v>
       </c>
     </row>
     <row r="10">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="F10" s="19" t="str">
-        <f>IF(OR(B10="",C10=""),"Informativo",IF(D10="Menor é melhor",IF(B10&lt;=C10,"No alvo",IF(B10&lt;=C10*1.1+(C10=0)*0.0001,"Perto","Fora")),IF(B10&gt;=C10,"No alvo",IF(B10&gt;=C10*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B10="",C10=""),"Informativo",IF(D10="Menor é melhor",IF(B10&lt;C10,"No alvo",IF(B10&lt;=C10*1.1+(C10=0)*0.0001,"Perto","Fora")),IF(B10&gt;C10,"No alvo",IF(B10&gt;=C10*0.9,"Perto","Fora"))))</f>
         <v>Informativo</v>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="F11" s="19" t="str">
-        <f>IF(OR(B11="",C11=""),"Informativo",IF(D11="Menor é melhor",IF(B11&lt;=C11,"No alvo",IF(B11&lt;=C11*1.1+(C11=0)*0.0001,"Perto","Fora")),IF(B11&gt;=C11,"No alvo",IF(B11&gt;=C11*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B11="",C11=""),"Informativo",IF(D11="Menor é melhor",IF(B11&lt;C11,"No alvo",IF(B11&lt;=C11*1.1+(C11=0)*0.0001,"Perto","Fora")),IF(B11&gt;C11,"No alvo",IF(B11&gt;=C11*0.9,"Perto","Fora"))))</f>
         <v>Informativo</v>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="F12" s="19" t="str">
-        <f>IF(OR(B12="",C12=""),"Informativo",IF(D12="Menor é melhor",IF(B12&lt;=C12,"No alvo",IF(B12&lt;=C12*1.1+(C12=0)*0.0001,"Perto","Fora")),IF(B12&gt;=C12,"No alvo",IF(B12&gt;=C12*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B12="",C12=""),"Informativo",IF(D12="Menor é melhor",IF(B12&lt;C12,"No alvo",IF(B12&lt;=C12*1.1+(C12=0)*0.0001,"Perto","Fora")),IF(B12&gt;C12,"No alvo",IF(B12&gt;=C12*0.9,"Perto","Fora"))))</f>
         <v>Informativo</v>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="F13" s="19" t="str">
-        <f>IF(OR(B13="",C13=""),"Informativo",IF(D13="Menor é melhor",IF(B13&lt;=C13,"No alvo",IF(B13&lt;=C13*1.1+(C13=0)*0.0001,"Perto","Fora")),IF(B13&gt;=C13,"No alvo",IF(B13&gt;=C13*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B13="",C13=""),"Informativo",IF(D13="Menor é melhor",IF(B13&lt;C13,"No alvo",IF(B13&lt;=C13*1.1+(C13=0)*0.0001,"Perto","Fora")),IF(B13&gt;C13,"No alvo",IF(B13&gt;=C13*0.9,"Perto","Fora"))))</f>
         <v>Informativo</v>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="F14" s="19" t="str">
-        <f>IF(OR(B14="",C14=""),"Informativo",IF(D14="Menor é melhor",IF(B14&lt;=C14,"No alvo",IF(B14&lt;=C14*1.1+(C14=0)*0.0001,"Perto","Fora")),IF(B14&gt;=C14,"No alvo",IF(B14&gt;=C14*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B14="",C14=""),"Informativo",IF(D14="Menor é melhor",IF(B14&lt;C14,"No alvo",IF(B14&lt;=C14*1.1+(C14=0)*0.0001,"Perto","Fora")),IF(B14&gt;C14,"No alvo",IF(B14&gt;=C14*0.9,"Perto","Fora"))))</f>
         <v>Fora</v>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="F15" s="19" t="str">
-        <f>IF(OR(B15="",C15=""),"Informativo",IF(D15="Menor é melhor",IF(B15&lt;=C15,"No alvo",IF(B15&lt;=C15*1.1+(C15=0)*0.0001,"Perto","Fora")),IF(B15&gt;=C15,"No alvo",IF(B15&gt;=C15*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B15="",C15=""),"Informativo",IF(D15="Menor é melhor",IF(B15&lt;C15,"No alvo",IF(B15&lt;=C15*1.1+(C15=0)*0.0001,"Perto","Fora")),IF(B15&gt;C15,"No alvo",IF(B15&gt;=C15*0.9,"Perto","Fora"))))</f>
         <v>Fora</v>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F16" s="19" t="str">
-        <f>IF(OR(B16="",C16=""),"Informativo",IF(D16="Menor é melhor",IF(B16&lt;=C16,"No alvo",IF(B16&lt;=C16*1.1+(C16=0)*0.0001,"Perto","Fora")),IF(B16&gt;=C16,"No alvo",IF(B16&gt;=C16*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B16="",C16=""),"Informativo",IF(D16="Menor é melhor",IF(B16&lt;C16,"No alvo",IF(B16&lt;=C16*1.1+(C16=0)*0.0001,"Perto","Fora")),IF(B16&gt;C16,"No alvo",IF(B16&gt;=C16*0.9,"Perto","Fora"))))</f>
         <v>No alvo</v>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="F17" s="19" t="str">
-        <f>IF(OR(B17="",C17=""),"Informativo",IF(D17="Menor é melhor",IF(B17&lt;=C17,"No alvo",IF(B17&lt;=C17*1.1+(C17=0)*0.0001,"Perto","Fora")),IF(B17&gt;=C17,"No alvo",IF(B17&gt;=C17*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B17="",C17=""),"Informativo",IF(D17="Menor é melhor",IF(B17&lt;C17,"No alvo",IF(B17&lt;=C17*1.1+(C17=0)*0.0001,"Perto","Fora")),IF(B17&gt;C17,"No alvo",IF(B17&gt;=C17*0.9,"Perto","Fora"))))</f>
         <v>Fora</v>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="F18" s="19" t="str">
-        <f>IF(OR(B18="",C18=""),"Informativo",IF(D18="Menor é melhor",IF(B18&lt;=C18,"No alvo",IF(B18&lt;=C18*1.1+(C18=0)*0.0001,"Perto","Fora")),IF(B18&gt;=C18,"No alvo",IF(B18&gt;=C18*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B18="",C18=""),"Informativo",IF(D18="Menor é melhor",IF(B18&lt;C18,"No alvo",IF(B18&lt;=C18*1.1+(C18=0)*0.0001,"Perto","Fora")),IF(B18&gt;C18,"No alvo",IF(B18&gt;=C18*0.9,"Perto","Fora"))))</f>
         <v>Informativo</v>
       </c>
     </row>
@@ -2805,14 +2805,14 @@
         </is>
       </c>
       <c r="F19" s="19" t="str">
-        <f>IF(OR(B19="",C19=""),"Informativo",IF(D19="Menor é melhor",IF(B19&lt;=C19,"No alvo",IF(B19&lt;=C19*1.1+(C19=0)*0.0001,"Perto","Fora")),IF(B19&gt;=C19,"No alvo",IF(B19&gt;=C19*0.9,"Perto","Fora"))))</f>
+        <f>IF(OR(B19="",C19=""),"Informativo",IF(D19="Menor é melhor",IF(B19&lt;C19,"No alvo",IF(B19&lt;=C19*1.1+(C19=0)*0.0001,"Perto","Fora")),IF(B19&gt;C19,"No alvo",IF(B19&gt;=C19*0.9,"Perto","Fora"))))</f>
         <v>Informativo</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>Linha sem limite fica "Informativo". "Perto" é até 10% do limite. Inadimplência = vencido ÷ (pago + vencido), a mesma conta da planilha 14. Convênio a receber é o que foi enviado e ainda está no prazo: informativo; o problema é o atrasado. Orçamentos em aberto também são informativos: pouco orçamento pendente pode ser bom (fechou tudo) ou ruim (a recepção parou de apresentar) — quem diz é a taxa de aprovação da planilha 15, não o valor parado. Os valores desta sexta valem para o mês escolhido em Config; no fim do mês, copie a coluna B para a linha do mês em Histórico.</t>
+          <t>Linha sem limite fica "Informativo". "Perto" é o limite exato ou até 10% além dele. Inadimplência = vencido ÷ (pago + vencido), a mesma conta da planilha 14. Convênio a receber é o que foi enviado e ainda está no prazo: informativo; o problema é o atrasado. Orçamentos em aberto também são informativos: pouco orçamento pendente pode ser bom (fechou tudo) ou ruim (a recepção parou de apresentar) — quem diz é a taxa de aprovação da planilha 15, não o valor parado. Os valores desta sexta valem para o mês escolhido em Config; no fim do mês, copie a coluna B para a linha do mês em Histórico.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
@@ -20,13 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="168" formatCode="+0.0&quot; p.p.&quot;;-0.0&quot; p.p.&quot;;0.0&quot; p.p.&quot;"/>
-    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%;0.0%"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="169" formatCode="+0.0&quot; p.p.&quot;;-0.0&quot; p.p.&quot;;0.0&quot; p.p.&quot;"/>
+    <numFmt numFmtId="170" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -209,16 +210,16 @@
     <xf numFmtId="9" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,22 +234,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -263,7 +264,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -276,11 +277,11 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -288,7 +289,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1075,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1236,17 +1237,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1387,7 +1400,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="13">
         <f>IF(Dados!$B$10="","—",Dados!$B$10)</f>
-        <v>21920</v>
+        <v>20710</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="13">
@@ -1397,7 +1410,7 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="13">
         <f>IF(Dados!$B$12="","—",Dados!$B$12)</f>
-        <v>8290</v>
+        <v>7080</v>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="13">
@@ -1662,7 +1675,7 @@
       <c r="B21" s="16" t="n"/>
       <c r="C21" s="25">
         <f>IF(Dados!B10="","—",Dados!B10)</f>
-        <v>21920</v>
+        <v>20710</v>
       </c>
       <c r="D21" s="25" t="str">
         <f>IF(Dados!C10="","—",Dados!C10)</f>
@@ -1674,7 +1687,7 @@
       </c>
       <c r="F21" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$G$5:$G$16,Config!$B$8-1)="","—",INDEX(Histórico!$G$5:$G$16,Config!$B$8-1)))</f>
-        <v>49651</v>
+        <v>55841</v>
       </c>
       <c r="G21" s="22" t="str">
         <f>IF(Config!$B$10&lt;&gt;"Sim","no fechamento",IF(OR(C21="—",F21="—",F21=0),"—",(C21-F21)/ABS(F21)))</f>
@@ -1701,7 +1714,7 @@
       </c>
       <c r="F22" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$H$5:$H$16,Config!$B$8-1)="","—",INDEX(Histórico!$H$5:$H$16,Config!$B$8-1)))</f>
-        <v>41660.12</v>
+        <v>40868.61</v>
       </c>
       <c r="G22" s="22" t="str">
         <f>IF(Config!$B$10&lt;&gt;"Sim","no fechamento",IF(OR(C22="—",F22="—",F22=0),"—",(C22-F22)/ABS(F22)))</f>
@@ -1716,7 +1729,7 @@
       <c r="B23" s="16" t="n"/>
       <c r="C23" s="25">
         <f>IF(Dados!B12="","—",Dados!B12)</f>
-        <v>8290</v>
+        <v>7080</v>
       </c>
       <c r="D23" s="25" t="str">
         <f>IF(Dados!C12="","—",Dados!C12)</f>
@@ -1728,7 +1741,7 @@
       </c>
       <c r="F23" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$I$5:$I$16,Config!$B$8-1)="","—",INDEX(Histórico!$I$5:$I$16,Config!$B$8-1)))</f>
-        <v>7990.88</v>
+        <v>14972.39</v>
       </c>
       <c r="G23" s="22" t="str">
         <f>IF(Config!$B$10&lt;&gt;"Sim","no fechamento",IF(OR(C23="—",F23="—",F23=0),"—",(C23-F23)/ABS(F23)))</f>
@@ -2259,9 +2272,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B7" s="32">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B7" s="32" t="n">
+        <v>46279</v>
       </c>
       <c r="D7" s="31" t="inlineStr">
         <is>
@@ -2581,7 +2593,7 @@
         </is>
       </c>
       <c r="B10" s="40" t="n">
-        <v>21920</v>
+        <v>20710</v>
       </c>
       <c r="C10" s="40" t="n"/>
       <c r="D10" s="35" t="inlineStr"/>
@@ -2624,7 +2636,7 @@
       </c>
       <c r="B12" s="25">
         <f>IF(OR(B10="",B11=""),"",B10-B11)</f>
-        <v>8290</v>
+        <v>7080</v>
       </c>
       <c r="C12" s="40" t="n"/>
       <c r="D12" s="35" t="inlineStr"/>
@@ -2986,14 +2998,14 @@
       <c r="E5" s="38" t="n"/>
       <c r="F5" s="39" t="n"/>
       <c r="G5" s="40" t="n">
-        <v>33270</v>
+        <v>25310</v>
       </c>
       <c r="H5" s="40" t="n">
-        <v>36200.56</v>
+        <v>35932.05</v>
       </c>
       <c r="I5" s="25">
         <f>IF(OR(G5="",H5=""),"",G5-H5)</f>
-        <v>-2930.56</v>
+        <v>-10622.05</v>
       </c>
       <c r="J5" s="40" t="n">
         <v>8740</v>
@@ -3025,14 +3037,14 @@
       <c r="E6" s="38" t="n"/>
       <c r="F6" s="39" t="n"/>
       <c r="G6" s="40" t="n">
-        <v>24795</v>
+        <v>25650</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>37090.28</v>
+        <v>36230.54</v>
       </c>
       <c r="I6" s="25">
         <f>IF(OR(G6="",H6=""),"",G6-H6)</f>
-        <v>-12295.28</v>
+        <v>-10580.54</v>
       </c>
       <c r="J6" s="40" t="n">
         <v>8350</v>
@@ -3064,14 +3076,14 @@
       <c r="E7" s="38" t="n"/>
       <c r="F7" s="39" t="n"/>
       <c r="G7" s="40" t="n">
-        <v>48330</v>
+        <v>40540</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>38415.25</v>
+        <v>38251.13</v>
       </c>
       <c r="I7" s="25">
         <f>IF(OR(G7="",H7=""),"",G7-H7)</f>
-        <v>9914.75</v>
+        <v>2288.87</v>
       </c>
       <c r="J7" s="40" t="n">
         <v>7836</v>
@@ -3103,14 +3115,14 @@
       <c r="E8" s="38" t="n"/>
       <c r="F8" s="39" t="n"/>
       <c r="G8" s="40" t="n">
-        <v>39555</v>
+        <v>40775</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>41061.7</v>
+        <v>40254.1</v>
       </c>
       <c r="I8" s="25">
         <f>IF(OR(G8="",H8=""),"",G8-H8)</f>
-        <v>-1506.7</v>
+        <v>520.900000000002</v>
       </c>
       <c r="J8" s="40" t="n">
         <v>13011</v>
@@ -3142,14 +3154,14 @@
       <c r="E9" s="38" t="n"/>
       <c r="F9" s="39" t="n"/>
       <c r="G9" s="40" t="n">
-        <v>44745</v>
+        <v>45380</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>39972.12</v>
+        <v>40120.29</v>
       </c>
       <c r="I9" s="25">
         <f>IF(OR(G9="",H9=""),"",G9-H9)</f>
-        <v>4772.88</v>
+        <v>5259.71</v>
       </c>
       <c r="J9" s="40" t="n">
         <v>9973</v>
@@ -3191,14 +3203,14 @@
         <v>0</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>44160</v>
+        <v>47240</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>41531.91</v>
+        <v>41702.87</v>
       </c>
       <c r="I10" s="25">
         <f>IF(OR(G10="",H10=""),"",G10-H10)</f>
-        <v>2628.09</v>
+        <v>5537.13</v>
       </c>
       <c r="J10" s="40" t="n">
         <v>12239</v>
@@ -3244,14 +3256,14 @@
         <v>1</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>53461</v>
+        <v>44471</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>43566.77</v>
+        <v>46321.6</v>
       </c>
       <c r="I11" s="25">
         <f>IF(OR(G11="",H11=""),"",G11-H11)</f>
-        <v>9894.23</v>
+        <v>-1850.6</v>
       </c>
       <c r="J11" s="40" t="n">
         <v>13553</v>
@@ -3297,14 +3309,14 @@
         <v>4</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>49651</v>
+        <v>55841</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>41660.12</v>
+        <v>40868.61</v>
       </c>
       <c r="I12" s="25">
         <f>IF(OR(G12="",H12=""),"",G12-H12)</f>
-        <v>7990.88</v>
+        <v>14972.39</v>
       </c>
       <c r="J12" s="40" t="n">
         <v>12077</v>
@@ -3350,14 +3362,14 @@
         <v>8</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>21920</v>
+        <v>20710</v>
       </c>
       <c r="H13" s="40" t="n">
         <v>13630</v>
       </c>
       <c r="I13" s="25">
         <f>IF(OR(G13="",H13=""),"",G13-H13)</f>
-        <v>8290</v>
+        <v>7080</v>
       </c>
       <c r="J13" s="40" t="n">
         <v>15758</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Escolha o mês do painel e mantenha a data de referência em =HOJE(). O título do Painel se ajusta.</t>
+          <t>Escolha o mês do painel e troque a data de referência por =HOJE() (no exemplo ela está congelada em 14/09/2026). O título do Painel se ajusta.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2010,167 +2010,167 @@
   </mergeCells>
   <conditionalFormatting sqref="A5">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>Dados!$F$5="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$5")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>Dados!$F$5="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$5")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>Dados!$F$5="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$5")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
     <cfRule type="expression" priority="4" dxfId="0">
-      <formula>Dados!$F$6="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$6")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1">
-      <formula>Dados!$F$6="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$6")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="2">
-      <formula>Dados!$F$6="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$6")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
     <cfRule type="expression" priority="7" dxfId="0">
-      <formula>Dados!$F$7="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$7")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="1">
-      <formula>Dados!$F$7="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$7")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="2">
-      <formula>Dados!$F$7="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$7")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
     <cfRule type="expression" priority="10" dxfId="0">
-      <formula>Dados!$F$8="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$8")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="11" dxfId="1">
-      <formula>Dados!$F$8="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$8")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="2">
-      <formula>Dados!$F$8="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$8")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
     <cfRule type="expression" priority="13" dxfId="0">
-      <formula>Dados!$F$9="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$9")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="14" dxfId="1">
-      <formula>Dados!$F$9="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$9")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="2">
-      <formula>Dados!$F$9="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$9")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
     <cfRule type="expression" priority="16" dxfId="0">
-      <formula>Dados!$F$10="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$10")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="17" dxfId="1">
-      <formula>Dados!$F$10="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$10")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="18" dxfId="2">
-      <formula>Dados!$F$10="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$10")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="19" dxfId="0">
-      <formula>Dados!$F$11="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$11")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="20" dxfId="1">
-      <formula>Dados!$F$11="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$11")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="21" dxfId="2">
-      <formula>Dados!$F$11="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$11")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
     <cfRule type="expression" priority="22" dxfId="0">
-      <formula>Dados!$F$12="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$12")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="23" dxfId="1">
-      <formula>Dados!$F$12="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$12")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="24" dxfId="2">
-      <formula>Dados!$F$12="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$12")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
     <cfRule type="expression" priority="25" dxfId="0">
-      <formula>Dados!$F$13="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$13")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="26" dxfId="1">
-      <formula>Dados!$F$13="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$13")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="27" dxfId="2">
-      <formula>Dados!$F$13="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$13")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
     <cfRule type="expression" priority="28" dxfId="0">
-      <formula>Dados!$F$14="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$14")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="29" dxfId="1">
-      <formula>Dados!$F$14="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$14")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="30" dxfId="2">
-      <formula>Dados!$F$14="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$14")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
     <cfRule type="expression" priority="31" dxfId="0">
-      <formula>Dados!$F$15="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$15")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="32" dxfId="1">
-      <formula>Dados!$F$15="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$15")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="33" dxfId="2">
-      <formula>Dados!$F$15="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$15")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11">
     <cfRule type="expression" priority="34" dxfId="0">
-      <formula>Dados!$F$16="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$16")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="35" dxfId="1">
-      <formula>Dados!$F$16="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$16")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="36" dxfId="2">
-      <formula>Dados!$F$16="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$16")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
     <cfRule type="expression" priority="37" dxfId="0">
-      <formula>Dados!$F$17="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$17")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="38" dxfId="1">
-      <formula>Dados!$F$17="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$17")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="39" dxfId="2">
-      <formula>Dados!$F$17="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$17")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
     <cfRule type="expression" priority="40" dxfId="0">
-      <formula>Dados!$F$18="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$18")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="41" dxfId="1">
-      <formula>Dados!$F$18="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$18")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="42" dxfId="2">
-      <formula>Dados!$F$18="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$18")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11">
     <cfRule type="expression" priority="43" dxfId="0">
-      <formula>Dados!$F$19="Fora"</formula>
+      <formula>INDIRECT("Dados!$F$19")="Fora"</formula>
     </cfRule>
     <cfRule type="expression" priority="44" dxfId="1">
-      <formula>Dados!$F$19="Perto"</formula>
+      <formula>INDIRECT("Dados!$F$19")="Perto"</formula>
     </cfRule>
     <cfRule type="expression" priority="45" dxfId="2">
-      <formula>Dados!$F$19="No alvo"</formula>
+      <formula>INDIRECT("Dados!$F$19")="No alvo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16:E30">
@@ -3484,7 +3484,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A5:A16">
     <cfRule type="expression" priority="1" dxfId="6">
-      <formula>ROW()-4=Config!$B$8</formula>
+      <formula>ROW()-4=INDIRECT("Config!$B$8")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="F22" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$H$5:$H$16,Config!$B$8-1)="","—",INDEX(Histórico!$H$5:$H$16,Config!$B$8-1)))</f>
-        <v>40868.61</v>
+        <v>40868.6</v>
       </c>
       <c r="G22" s="22" t="str">
         <f>IF(Config!$B$10&lt;&gt;"Sim","no fechamento",IF(OR(C22="—",F22="—",F22=0),"—",(C22-F22)/ABS(F22)))</f>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F23" s="25">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Histórico!$I$5:$I$16,Config!$B$8-1)="","—",INDEX(Histórico!$I$5:$I$16,Config!$B$8-1)))</f>
-        <v>14972.39</v>
+        <v>14972.4</v>
       </c>
       <c r="G23" s="22" t="str">
         <f>IF(Config!$B$10&lt;&gt;"Sim","no fechamento",IF(OR(C23="—",F23="—",F23=0),"—",(C23-F23)/ABS(F23)))</f>
@@ -3040,11 +3040,11 @@
         <v>25650</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>36230.54</v>
+        <v>36230.55</v>
       </c>
       <c r="I6" s="25">
         <f>IF(OR(G6="",H6=""),"",G6-H6)</f>
-        <v>-10580.54</v>
+        <v>-10580.55</v>
       </c>
       <c r="J6" s="40" t="n">
         <v>8350</v>
@@ -3118,11 +3118,11 @@
         <v>40775</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>40254.1</v>
+        <v>40254.11</v>
       </c>
       <c r="I8" s="25">
         <f>IF(OR(G8="",H8=""),"",G8-H8)</f>
-        <v>520.900000000002</v>
+        <v>520.889999999999</v>
       </c>
       <c r="J8" s="40" t="n">
         <v>13011</v>
@@ -3157,11 +3157,11 @@
         <v>45380</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>40120.29</v>
+        <v>40120.27</v>
       </c>
       <c r="I9" s="25">
         <f>IF(OR(G9="",H9=""),"",G9-H9)</f>
-        <v>5259.71</v>
+        <v>5259.73</v>
       </c>
       <c r="J9" s="40" t="n">
         <v>9973</v>
@@ -3259,11 +3259,11 @@
         <v>44471</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>46321.6</v>
+        <v>46321.61</v>
       </c>
       <c r="I11" s="25">
         <f>IF(OR(G11="",H11=""),"",G11-H11)</f>
-        <v>-1850.6</v>
+        <v>-1850.61</v>
       </c>
       <c r="J11" s="40" t="n">
         <v>13553</v>
@@ -3312,11 +3312,11 @@
         <v>55841</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>40868.61</v>
+        <v>40868.6</v>
       </c>
       <c r="I12" s="25">
         <f>IF(OR(G12="",H12=""),"",G12-H12)</f>
-        <v>14972.39</v>
+        <v>14972.4</v>
       </c>
       <c r="J12" s="40" t="n">
         <v>12077</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/17-painel-da-clinica.xlsx
@@ -1300,7 +1300,7 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="str">
-        <f>"Nada para digitar aqui. Os números vêm da aba Dados (atualizada toda sexta) e o mês anterior vem do Histórico. Referência: "&amp;TEXT(Config!B7,"dd/mm/yyyy")&amp;"."</f>
+        <f>"Nada para digitar aqui. Os números vêm da aba Dados (atualizada toda sexta) e o mês anterior vem do Histórico. Referência: "&amp;TEXT(DAY(Config!B7),"00")&amp;"/"&amp;TEXT(MONTH(Config!B7),"00")&amp;"/"&amp;YEAR(Config!B7)&amp;"."</f>
         <v>Nada para digitar aqui. Os números vêm da aba Dados (atualizada toda sexta) e o mês anterior vem do Histórico. Referência: 14/09/2026.</v>
       </c>
     </row>
